--- a/template/header_template.xlsx
+++ b/template/header_template.xlsx
@@ -1043,7 +1043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI4"/>
+  <dimension ref="A1:BP4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="19.75" customWidth="1" style="5" min="1" max="1"/>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC1" s="3" t="inlineStr">
         <is>
-          <t>伊奈川合流地点</t>
+          <t>伊南川合流地点</t>
         </is>
       </c>
       <c r="AD1" s="2" t="inlineStr">
@@ -1259,94 +1259,88 @@
           <t>麻生大橋</t>
         </is>
       </c>
-      <c r="AR1" s="3" t="inlineStr">
-        <is>
-          <t>（のぞ
-み橋）</t>
-        </is>
-      </c>
-      <c r="AS1" s="2" t="inlineStr">
+      <c r="AR1" s="2" t="inlineStr">
         <is>
           <t>大野橋</t>
         </is>
       </c>
+      <c r="AS1" s="3" t="inlineStr">
+        <is>
+          <t>弁天橋</t>
+        </is>
+      </c>
       <c r="AT1" s="3" t="inlineStr">
         <is>
-          <t>弁天橋</t>
+          <t>青柳橋</t>
         </is>
       </c>
       <c r="AU1" s="3" t="inlineStr">
         <is>
-          <t>青柳橋</t>
+          <t>下山橋</t>
         </is>
       </c>
       <c r="AV1" s="3" t="inlineStr">
         <is>
-          <t>下山橋</t>
+          <t>中の橋</t>
         </is>
       </c>
       <c r="AW1" s="3" t="inlineStr">
         <is>
-          <t>中の橋</t>
+          <t>萬歳橋</t>
         </is>
       </c>
       <c r="AX1" s="3" t="inlineStr">
         <is>
-          <t>萬歳橋</t>
+          <t>赤岩橋</t>
         </is>
       </c>
       <c r="AY1" s="3" t="inlineStr">
         <is>
-          <t>赤岩橋</t>
+          <t>滝沢橋</t>
         </is>
       </c>
       <c r="AZ1" s="3" t="inlineStr">
         <is>
-          <t>滝沢橋</t>
+          <t>木賊</t>
         </is>
       </c>
       <c r="BA1" s="3" t="inlineStr">
         <is>
-          <t>木賊</t>
+          <t>七入橋</t>
         </is>
       </c>
       <c r="BB1" s="3" t="inlineStr">
         <is>
-          <t>七入橋</t>
+          <t>前川橋</t>
         </is>
       </c>
       <c r="BC1" s="3" t="inlineStr">
         <is>
-          <t>前川橋</t>
+          <t>大宮橋</t>
         </is>
       </c>
       <c r="BD1" s="3" t="inlineStr">
-        <is>
-          <t>大宮橋</t>
-        </is>
-      </c>
-      <c r="BE1" s="3" t="inlineStr">
         <is>
           <t>内川
 ロック</t>
         </is>
       </c>
-      <c r="BF1" s="3" t="inlineStr">
+      <c r="BE1" s="3" t="inlineStr">
         <is>
           <t>倭橋</t>
         </is>
       </c>
-      <c r="BG1" s="2" t="inlineStr">
+      <c r="BF1" s="2" t="inlineStr">
         <is>
           <t>鹿島橋</t>
         </is>
       </c>
+      <c r="BG1" s="3" t="inlineStr">
+        <is>
+          <t>待侘橋</t>
+        </is>
+      </c>
       <c r="BH1" s="3" t="inlineStr">
-        <is>
-          <t>待侘橋</t>
-        </is>
-      </c>
-      <c r="BI1" s="3" t="inlineStr">
         <is>
           <t>小川橋</t>
         </is>

--- a/template/header_template.xlsx
+++ b/template/header_template.xlsx
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC1" s="3" t="inlineStr">
         <is>
-          <t>伊南川合流地点</t>
+          <t>伊南川合流部</t>
         </is>
       </c>
       <c r="AD1" s="2" t="inlineStr">
@@ -1233,114 +1233,108 @@
           <t>西谷橋</t>
         </is>
       </c>
-      <c r="AM1" s="2" t="inlineStr">
-        <is>
-          <t>（川口橋）</t>
-        </is>
-      </c>
-      <c r="AN1" s="3" t="inlineStr">
+      <c r="AM1" s="3" t="inlineStr">
         <is>
           <t>金山ふれ
 あい広場</t>
         </is>
       </c>
+      <c r="AN1" s="2" t="inlineStr">
+        <is>
+          <t>早戸大橋</t>
+        </is>
+      </c>
       <c r="AO1" s="2" t="inlineStr">
         <is>
-          <t>早戸大橋</t>
+          <t>三島大橋</t>
         </is>
       </c>
       <c r="AP1" s="2" t="inlineStr">
         <is>
-          <t>三島大橋</t>
+          <t>麻生大橋</t>
         </is>
       </c>
       <c r="AQ1" s="2" t="inlineStr">
         <is>
-          <t>麻生大橋</t>
-        </is>
-      </c>
-      <c r="AR1" s="2" t="inlineStr">
-        <is>
           <t>大野橋</t>
         </is>
       </c>
+      <c r="AR1" s="3" t="inlineStr">
+        <is>
+          <t>弁天橋</t>
+        </is>
+      </c>
       <c r="AS1" s="3" t="inlineStr">
         <is>
-          <t>弁天橋</t>
+          <t>青柳橋</t>
         </is>
       </c>
       <c r="AT1" s="3" t="inlineStr">
         <is>
-          <t>青柳橋</t>
+          <t>下山橋</t>
         </is>
       </c>
       <c r="AU1" s="3" t="inlineStr">
         <is>
-          <t>下山橋</t>
+          <t>中の橋</t>
         </is>
       </c>
       <c r="AV1" s="3" t="inlineStr">
         <is>
-          <t>中の橋</t>
+          <t>萬歳橋</t>
         </is>
       </c>
       <c r="AW1" s="3" t="inlineStr">
         <is>
-          <t>萬歳橋</t>
+          <t>赤岩橋</t>
         </is>
       </c>
       <c r="AX1" s="3" t="inlineStr">
         <is>
-          <t>赤岩橋</t>
+          <t>滝沢橋</t>
         </is>
       </c>
       <c r="AY1" s="3" t="inlineStr">
         <is>
-          <t>滝沢橋</t>
+          <t>木賊</t>
         </is>
       </c>
       <c r="AZ1" s="3" t="inlineStr">
         <is>
-          <t>木賊</t>
+          <t>七入橋</t>
         </is>
       </c>
       <c r="BA1" s="3" t="inlineStr">
         <is>
-          <t>七入橋</t>
+          <t>前川橋</t>
         </is>
       </c>
       <c r="BB1" s="3" t="inlineStr">
         <is>
-          <t>前川橋</t>
+          <t>大宮橋</t>
         </is>
       </c>
       <c r="BC1" s="3" t="inlineStr">
         <is>
-          <t>大宮橋</t>
+          <t>内川ロックジェット</t>
         </is>
       </c>
       <c r="BD1" s="3" t="inlineStr">
         <is>
-          <t>内川
-ロック</t>
-        </is>
-      </c>
-      <c r="BE1" s="3" t="inlineStr">
-        <is>
           <t>倭橋</t>
         </is>
       </c>
-      <c r="BF1" s="2" t="inlineStr">
+      <c r="BE1" s="2" t="inlineStr">
         <is>
           <t>鹿島橋</t>
         </is>
       </c>
+      <c r="BF1" s="3" t="inlineStr">
+        <is>
+          <t>待侘橋</t>
+        </is>
+      </c>
       <c r="BG1" s="3" t="inlineStr">
-        <is>
-          <t>待侘橋</t>
-        </is>
-      </c>
-      <c r="BH1" s="3" t="inlineStr">
         <is>
           <t>小川橋</t>
         </is>
